--- a/agrra_monitoring/data_raw/ATG_NEMMA_2025/Calculated/FishSizeFreq.xlsx
+++ b/agrra_monitoring/data_raw/ATG_NEMMA_2025/Calculated/FishSizeFreq.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\ATG\Calculated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AGRRA Group Work\Data Product Fix\Ruleo\NEMMA&amp;CadesReef2025\Calculated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06CBFA6A-82F1-4B27-BA64-676C21744C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937CEE99-6C2A-4CC7-94DC-DEAD26E1EDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TermsOfUse" sheetId="24" r:id="rId1"/>
+    <sheet name="TermsOfUse" sheetId="25" r:id="rId1"/>
     <sheet name="Metadata" sheetId="1" r:id="rId2"/>
     <sheet name="Overall" sheetId="2" r:id="rId3"/>
     <sheet name="tACAN" sheetId="3" r:id="rId4"/>
@@ -38,7 +38,7 @@
     <sheet name="tTETR" sheetId="22" r:id="rId23"/>
     <sheet name="UNKN" sheetId="23" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -735,12 +735,40 @@
     <t>200cm+std</t>
   </si>
   <si>
-    <t>Created: 2025 May 29</t>
+    <t>Created: 2026 May 29</t>
   </si>
   <si>
-    <t>Version 1.0</t>
+    <t>AGRRA Terms of Data Service</t>
   </si>
   <si>
+    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae, and fishes, and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA’s goal is to provide data contributors access to the AGRRA data platform, which provides: 
+a)	a standardized way to enter coral reef monitoring data with built in quality controls,
+b)	an efficient way to process data and visualize data through interactive graphics,
+c)	synthesized data products provided as RAW data and Calculated Products, and 
+d)	a centralized and secure place to manage and store data.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Ownership &amp; Intellectual Property</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -750,23 +778,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Date produced: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Data in this country batch were produced in collaboration with the batch owner: Margaret Wilson. These data products are in draft form and are under review. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Data License below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use. </t>
-    </r>
-  </si>
-  <si>
-    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae and fishes and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Conditions of Use of AGRRA Data Products
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -775,7 +787,330 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">In order to use the AGRRA dataset, you need to accept the Terms and Conditions in the AGRRA Data License below.
+      <t xml:space="preserve">•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Original Observations:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> The raw data collected during surveys remains the intellectual property of the original data collectors and their respective organizations.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Methodology &amp; Systems: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">All protocols (Benthic, Coral, Fish), platform systems, AGRRA content, and related tools remain the intellectual property of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ocean Research &amp; Education Foundation, Inc. (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, and their licensors, as applicable.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Processed Metrics: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">The calculated metrics, custom-coded logic, and standardized protocols used to generate these spreadsheets are the proprietary property of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ocean Research &amp; Education Foundation (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">User Content: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Users retain ownership of data, images, and other content they submit, but grant AGRRA the rights needed to store, process, share, and display that content in accordance with these terms.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Data Sharing &amp; Privacy Publication Protocol
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA is committed to protecting the privacy of the Data Contributors with respect to their data batches and offers three privacy options for each data batch:
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Batch Privacy Options: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Data Batches may be designated as Private, Public Summary, or Public. Some batch metadata may remain publicly visible to support transparency and attribution.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accounts &amp; Security:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors are responsible for their accounts, passwords, and all activity under their accounts, and must promptly report any suspected unauthorized access.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Permitted Uses</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+•	Non-Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors and Third-party Users (with permission) are licensed to use these materials and datasets for research, education, conservation, and other non-commercial purposes.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Commercial use, sale, or redistribution of AGRRA materials, datasets, or API outputs requires prior written permission.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lawful and Responsible Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> All users must comply with applicable laws and must not misuse, disrupt, alter, scrape, or interfere with the platform, its software, security, or other users.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. Citation &amp; Acknowledgment
 </t>
     </r>
     <r>
@@ -787,7 +1122,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>AGRRA Data License and Data Use Agreements</t>
+      <t>A. Guidance for Original Data Contributors</t>
     </r>
     <r>
       <rPr>
@@ -796,7 +1131,167 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-By accessing and using any of the datasets distributed by AGRRA, you acknowledge that you have read, understood, and agree to comply with the terms and conditions contained within this agreement. A Data Use Agreement (DUA) must be entered into before there is any use or distribution of a data set to an outside entity. AGRRA may amend these terms and conditions at any time. Your continued use of this data constitutes acceptance of the terms and conditions stated at the time of your use. You should contact AGRRA to determine the current terms and conditions to which you are bound.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to cite your data:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> When publishing, presenting, or otherwise sharing analyses based on your own contributed dataset, please cite the dataset using the suggested AGRRA format: [Surveyor Names/Organization], [Country] ([Year]). [Dataset Name/Region]. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, [Protocol Version Number] [Data Product Name]. [URL/DOI]. Accessed [Date].
+                o   Examples
+                         ▪For a specific survey: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Smith, J. &amp; Reef Care Bahamas, Bahamas (2024). New Providence Benthic Surveys. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, v5.2 Coral &amp; Benthic Data. www.agrra.org. Accessed May 14, 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+                         ▪For an aggregated country-level report: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Belize Fisheries Department &amp; Healthy Reefs Initiative, Belize (2025). 2025 National Monitoring Data. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform. www.agrra.org. Accessed May 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to acknowledge AGRRA:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> In all publications and presentations using your contributed data, please acknowledge AGRRA as the platform that curates, manages, and provides access to the dataset.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Suggested acknowledgment language:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> "We acknowledge (or thank) the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Contributors are encouraged to remain available for collaboration when their expertise may strengthen data interpretation or publication.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notification of use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Please share an electronic copy of any final reports, publications, or presentations with AGRRA curated data to data@agrra.org.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -808,7 +1303,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Permissions and Proprietary Rights to Content</t>
+      <t>B. Guidance for Third-Party Data Users</t>
     </r>
     <r>
       <rPr>
@@ -817,8 +1312,8 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-All datasets are the property of AGRRA and/or its affiliates, unless otherwise noted. With permission and DUA, you may use these datasets for non-commercial purposes, including research, education, presentations, and non-commercial publications. You understand and agree that you may not copy, reproduce, distribute or create derivative works for other purposes, without prior, written authorization from the AGRRA Project Leader. When using or publishing any parts of these datasets, proper acknowledgement of AGRRA and original source(s), is required.
-</t>
+Third-party users (not original data collectors) who would like to use an AGRRA data batch should first contact and obtain permission from the original data contributor and/or AGRRA at data@agrra.org. Once permission is granted, third-party users who utilize AGRRA-hosted data for research, presentations, reports, or publications shall give appropriate credit to both the original data contributors and AGRRA. The guidance below explains how to cite the original dataset and how to acknowledge AGRRA as the data platform.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -829,7 +1324,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Limitation of Liability</t>
+      <t xml:space="preserve">How to cite original data contributors: </t>
     </r>
     <r>
       <rPr>
@@ -837,9 +1332,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-AGRRA makes reasonable efforts to provide accurate data and information through its website, database, and other channels. Nevertheless, you understand and agree that AGRRA shall not be liable for any loss or damage resulting from any use of, or inability to use, this data, or resulting from any errors or omissions in the data content.
-</t>
+      <t xml:space="preserve">Cite the dataset using the names of the original surveyors, organizations, country, year, and dataset title, following the AGRRA dataset citation format. AGRRA can provide guidance on the appropriate citation for the specific dataset used.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -850,7 +1344,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Data Citation </t>
+      <t>How to acknowledge AGRRA:</t>
     </r>
     <r>
       <rPr>
@@ -858,9 +1352,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-For any use of AGRRA data or datasets managed by AGRRA, or for general reference to the project in peer-reviewed literature, use the citation specified in the data use policy or for general citation use the following format below to cite data retrieved from the AGRRA website or AGRRA database manager. 
-</t>
+      <t xml:space="preserve"> In addition to citing the original dataset, acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform as the system that curates, manages, and provides access to the data.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -871,7 +1364,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Citation:</t>
+      <t xml:space="preserve">Suggested acknowledgment language: </t>
     </r>
     <r>
       <rPr>
@@ -879,8 +1372,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> AGRRA. 2024. Atlantic and Gulf Rapid Reef Assessment (AGRRA): An online database of AGRRA coral reef survey data. Available: http://agrra.org. (Accessed: Date [e.g., March 10, 2024]).
-</t>
+      <t xml:space="preserve">"We thank the original data contributors [insert surveyor and/or organization names, where available] and acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
     </r>
     <r>
       <rPr>
@@ -891,7 +1384,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Acknowledgement:</t>
+      <t>Direct contact and collaboration:</t>
     </r>
     <r>
       <rPr>
@@ -899,11 +1392,30 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> For general data, use: “We thank the following data providers: Atlantic Gulf Rapid Reef Assessment (AGRRA) contributors and data managers…”. Where noted, individual data contributors should be included in acknowledgments. 
+      <t xml:space="preserve"> Third-party users are encouraged to contact the original data collectors to discuss collaboration or co-authorship, clarify interpretation, and share findings, where appropriate.
 </t>
     </r>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Liability &amp; Compliance
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">•	</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -913,7 +1425,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Use Policy</t>
+      <t>Data Integrity:</t>
     </r>
     <r>
       <rPr>
@@ -921,19 +1433,9 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-Data collected under the auspices of AGRRA are available to the public after primary publication, or at most two years after the completion of the study unless proprietary restrictions are warranted. Request for the use of AGRRA data is to be made in writing and is subject to acceptance of the following conditions:
-1. The user agrees to provide valid name and contact information prior to requesting or downloading online data. This information will be used to ensure data agreements are in place, to contact the user in case of changes to the data, and may also be used by data set authors and AGRRA project administrators to document data usage.
-2. The user agrees to cite the data set author (if stated) and AGRRA in all publications in which the data are used, as per the instructions in “Data Citation”. 
-3. The user agrees to provide one copy of any manuscript based on AGRRA data to the AGRRA or data set author (if specified) prior to submitting it for peer-reviewed publication.
-4. The user also agrees to send one electronic copy or reports or publication (pdf format) to: data@agrra.org and gis@agrra.org. 
-5. Users are prohibited from selling or redistributing any data provided by AGRRA without explicit prior permission.
-6. If specified, users are to contact original investigators or data contributors responsible for data prior to data use, and where appropriate, are encouraged to consider collaboration and/or co-authorship with original investigators.
-7. Extensive efforts are made to ensure that data products are accurate and up to date, but the authors and AGRRA will not take responsibility for any errors that may exist in data provided. The user assumes all responsibility for errors in analysis or judgment resulting from use of the data.
-8. Any violation of the terms of this agreement will result in immediate forfeiture of the data and loss of access privileges to other AGRRA data sets.  </t>
+      <t xml:space="preserve"> AGRRA works diligently to maintain data accuracy; however, Data Contributors and Third-Party users are responsible for their own analyses, interpretations, and resulting conclusions.
+•	</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -943,7 +1445,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Format of Data:</t>
+      <t>No Warranty:</t>
     </r>
     <r>
       <rPr>
@@ -951,8 +1453,71 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. Note these are draft data products from the beta version of the new AGRRA data portal (2024) and are currently in review. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
+      <t xml:space="preserve"> The platform, data, and related content are provided “as is” and “as available,” without guarantees of accuracy, availability, security, or fitness for a particular purpose.
+•	</t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limitation of Liability:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA and its operators are not liable for indirect, incidental, consequential, or data-loss-related damages arising from the use of the platform.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Access Review: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">If these terms are not followed, AGRRA reserves the right to review, suspend, modify, or terminate access privileges or service availability as appropriate.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Changes &amp; Governing Law:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA may update these terms from time to time; continued use represents acceptance. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
   </si>
   <si>
     <r>
@@ -976,23 +1541,30 @@
     </r>
   </si>
   <si>
+    <t>Version 1.0</t>
+  </si>
+  <si>
+    <t>Data provided in these country batches were produced in collaboration with the batch owner: Ruleo Camacho. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Terms of Data Service below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use.</t>
+  </si>
+  <si>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>©</t>
+      <t>Format of Data:</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Ocean Research and Education Foundation</t>
+      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
     </r>
   </si>
 </sst>
@@ -1000,11 +1572,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1028,16 +1607,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1060,7 +1658,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1078,6 +1676,66 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1087,7 +1745,22 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1210,16 +1883,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1238,126 +1912,117 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{6FB5600E-B171-4AFC-ABAF-440617151852}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{04DA0138-7491-49E2-BF4A-AE9FC675C6B2}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{80431DE5-5342-44CC-85F4-9B75121E5828}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -1370,61 +2035,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>322132</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8721EEE-40CF-4F08-9E83-DC6419F8740F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6276976" y="180976"/>
-          <a:ext cx="2655756" cy="2038350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1713,1051 +2323,1601 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BF25B9-4A8E-4A66-B8C6-F4D6B2B410E0}">
-  <dimension ref="A1:W78"/>
-  <sheetFormatPr defaultColWidth="9.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AFF377-DEA2-4C6E-980D-8FB43AC3AF01}">
+  <dimension ref="A1:X70"/>
+  <sheetFormatPr defaultColWidth="9.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="14" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="14" customWidth="1"/>
-    <col min="3" max="16384" width="9.7109375" style="14"/>
+    <col min="2" max="2" width="11.26953125" style="14" customWidth="1"/>
+    <col min="3" max="16384" width="9.7265625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>230</v>
       </c>
       <c r="B1" s="13"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" s="13"/>
+    </row>
+    <row r="4" spans="1:23" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B2" s="13"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="19"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="22"/>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:23" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="15"/>
-    </row>
-    <row r="15" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:23" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="25"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="18"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="28"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="31"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="31"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="31"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="31"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="31"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="31"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" s="29"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="31"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="29"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="31"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" s="29"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="31"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="31"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="31"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="31"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="31"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A24" s="29"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="31"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="31"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="31"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="31"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="31"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="31"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A30" s="29"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="31"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A31" s="29"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="31"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="31"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="31"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="30"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="31"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="31"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="31"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="31"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="31"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="30"/>
+      <c r="S39" s="30"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="30"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="31"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="31"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A41" s="29"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="30"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="30"/>
+      <c r="R41" s="30"/>
+      <c r="S41" s="30"/>
+      <c r="T41" s="30"/>
+      <c r="U41" s="30"/>
+      <c r="V41" s="30"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="22" t="s">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A42" s="29"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="31"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A43" s="29"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="31"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A44" s="29"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="30"/>
+      <c r="R44" s="30"/>
+      <c r="S44" s="30"/>
+      <c r="T44" s="30"/>
+      <c r="U44" s="30"/>
+      <c r="V44" s="30"/>
+      <c r="W44" s="31"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="30"/>
+      <c r="R45" s="30"/>
+      <c r="S45" s="30"/>
+      <c r="T45" s="30"/>
+      <c r="U45" s="30"/>
+      <c r="V45" s="30"/>
+      <c r="W45" s="31"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A46" s="29"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="31"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A47" s="29"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
+      <c r="S47" s="30"/>
+      <c r="T47" s="30"/>
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="31"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="29"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="30"/>
+      <c r="T48" s="30"/>
+      <c r="U48" s="30"/>
+      <c r="V48" s="30"/>
+      <c r="W48" s="31"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A49" s="29"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="31"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A50" s="29"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="30"/>
+      <c r="R50" s="30"/>
+      <c r="S50" s="30"/>
+      <c r="T50" s="30"/>
+      <c r="U50" s="30"/>
+      <c r="V50" s="30"/>
+      <c r="W50" s="31"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A51" s="29"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="S51" s="30"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="31"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A52" s="29"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="31"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A53" s="29"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30"/>
+      <c r="O53" s="30"/>
+      <c r="P53" s="30"/>
+      <c r="Q53" s="30"/>
+      <c r="R53" s="30"/>
+      <c r="S53" s="30"/>
+      <c r="T53" s="30"/>
+      <c r="U53" s="30"/>
+      <c r="V53" s="30"/>
+      <c r="W53" s="31"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A54" s="29"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
+      <c r="S54" s="30"/>
+      <c r="T54" s="30"/>
+      <c r="U54" s="30"/>
+      <c r="V54" s="30"/>
+      <c r="W54" s="31"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="31"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A56" s="29"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
+      <c r="N56" s="30"/>
+      <c r="O56" s="30"/>
+      <c r="P56" s="30"/>
+      <c r="Q56" s="30"/>
+      <c r="R56" s="30"/>
+      <c r="S56" s="30"/>
+      <c r="T56" s="30"/>
+      <c r="U56" s="30"/>
+      <c r="V56" s="30"/>
+      <c r="W56" s="31"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A57" s="29"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30"/>
+      <c r="O57" s="30"/>
+      <c r="P57" s="30"/>
+      <c r="Q57" s="30"/>
+      <c r="R57" s="30"/>
+      <c r="S57" s="30"/>
+      <c r="T57" s="30"/>
+      <c r="U57" s="30"/>
+      <c r="V57" s="30"/>
+      <c r="W57" s="31"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A58" s="29"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="31"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A59" s="29"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30"/>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="30"/>
+      <c r="R59" s="30"/>
+      <c r="S59" s="30"/>
+      <c r="T59" s="30"/>
+      <c r="U59" s="30"/>
+      <c r="V59" s="30"/>
+      <c r="W59" s="31"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A60" s="29"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30"/>
+      <c r="O60" s="30"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
+      <c r="S60" s="30"/>
+      <c r="T60" s="30"/>
+      <c r="U60" s="30"/>
+      <c r="V60" s="30"/>
+      <c r="W60" s="31"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A61" s="29"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="31"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A62" s="29"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
+      <c r="M62" s="30"/>
+      <c r="N62" s="30"/>
+      <c r="O62" s="30"/>
+      <c r="P62" s="30"/>
+      <c r="Q62" s="30"/>
+      <c r="R62" s="30"/>
+      <c r="S62" s="30"/>
+      <c r="T62" s="30"/>
+      <c r="U62" s="30"/>
+      <c r="V62" s="30"/>
+      <c r="W62" s="31"/>
+    </row>
+    <row r="63" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="32"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="33"/>
+      <c r="S63" s="33"/>
+      <c r="T63" s="33"/>
+      <c r="U63" s="33"/>
+      <c r="V63" s="33"/>
+      <c r="W63" s="34"/>
+    </row>
+    <row r="64" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="35"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A65" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" s="37"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="37"/>
+      <c r="I65" s="37"/>
+      <c r="J65" s="37"/>
+      <c r="K65" s="37"/>
+      <c r="L65" s="37"/>
+      <c r="M65" s="37"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="37"/>
+      <c r="R65" s="37"/>
+      <c r="S65" s="37"/>
+      <c r="T65" s="37"/>
+      <c r="U65" s="37"/>
+      <c r="V65" s="37"/>
+      <c r="W65" s="38"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="39"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="40"/>
+      <c r="M66" s="40"/>
+      <c r="N66" s="40"/>
+      <c r="O66" s="40"/>
+      <c r="P66" s="40"/>
+      <c r="Q66" s="40"/>
+      <c r="R66" s="40"/>
+      <c r="S66" s="40"/>
+      <c r="T66" s="40"/>
+      <c r="U66" s="40"/>
+      <c r="V66" s="40"/>
+      <c r="W66" s="41"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="24"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="30"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="29"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="30"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="30"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-      <c r="W21" s="30"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-      <c r="W22" s="30"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="30"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="30"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-      <c r="W25" s="30"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="30"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="30"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="30"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="30"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-      <c r="W30" s="30"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="29"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="29"/>
-      <c r="S31" s="29"/>
-      <c r="T31" s="29"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-      <c r="W31" s="30"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="30"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="25"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="29"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-      <c r="W33" s="30"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="29"/>
-      <c r="S34" s="29"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-      <c r="W34" s="30"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="29"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="30"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-      <c r="W36" s="30"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="30"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="25"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-      <c r="W38" s="30"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29"/>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29"/>
-      <c r="T39" s="29"/>
-      <c r="U39" s="29"/>
-      <c r="V39" s="29"/>
-      <c r="W39" s="30"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="30"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="25"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
-      <c r="W41" s="30"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29"/>
-      <c r="T42" s="29"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-      <c r="W42" s="30"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="25"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="30"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="25"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="29"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="29"/>
-      <c r="S44" s="29"/>
-      <c r="T44" s="29"/>
-      <c r="U44" s="29"/>
-      <c r="V44" s="29"/>
-      <c r="W44" s="30"/>
-    </row>
-    <row r="45" spans="1:23" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29"/>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="29"/>
-      <c r="R45" s="29"/>
-      <c r="S45" s="29"/>
-      <c r="T45" s="29"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="29"/>
-      <c r="W45" s="30"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="25"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="30"/>
-    </row>
-    <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="31"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
-      <c r="U47" s="35"/>
-      <c r="V47" s="35"/>
-      <c r="W47" s="36"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
-      <c r="K48" s="38"/>
-      <c r="L48" s="38"/>
-      <c r="M48" s="38"/>
-      <c r="N48" s="38"/>
-      <c r="O48" s="38"/>
-      <c r="P48" s="38"/>
-      <c r="Q48" s="38"/>
-      <c r="R48" s="38"/>
-      <c r="S48" s="38"/>
-      <c r="T48" s="38"/>
-      <c r="U48" s="38"/>
-      <c r="V48" s="38"/>
-      <c r="W48" s="39"/>
-    </row>
-    <row r="49" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="40"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-      <c r="N49" s="41"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="41"/>
-      <c r="S49" s="41"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="42"/>
-    </row>
-    <row r="50" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="44"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="44"/>
-      <c r="I50" s="44"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
-      <c r="M50" s="44"/>
-      <c r="N50" s="44"/>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44"/>
-      <c r="S50" s="44"/>
-      <c r="T50" s="44"/>
-      <c r="U50" s="44"/>
-      <c r="V50" s="44"/>
-      <c r="W50" s="45"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="S51" s="46" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A59" s="47"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A60" s="48"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A61" s="48"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A62" s="48"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A63" s="48"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A64" s="48"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="48"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="48"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="48"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="48"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="48"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="48"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="48"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="48"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="48"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="48"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="48"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="48"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="48"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="43"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="43"/>
+      <c r="L67" s="43"/>
+      <c r="M67" s="43"/>
+      <c r="N67" s="43"/>
+      <c r="O67" s="43"/>
+      <c r="P67" s="43"/>
+      <c r="Q67" s="43"/>
+      <c r="R67" s="43"/>
+      <c r="S67" s="43"/>
+      <c r="T67" s="43"/>
+      <c r="U67" s="43"/>
+      <c r="V67" s="43"/>
+      <c r="W67" s="44"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A68" s="35"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A69" s="35"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A70" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A48:W49"/>
-    <mergeCell ref="A50:W50"/>
+    <mergeCell ref="A65:W66"/>
+    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A13:W14"/>
-    <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A17:K47"/>
-    <mergeCell ref="L17:W47"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A6:W7"/>
+    <mergeCell ref="A9:W9"/>
+    <mergeCell ref="A10:W63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -2772,7 +3932,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -2978,7 +4138,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -3184,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -3201,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -3218,7 +4378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -3235,7 +4395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -3441,7 +4601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -3458,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -3475,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -3681,7 +4841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -3707,7 +4867,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -3722,7 +4882,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -3928,7 +5088,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -4134,7 +5294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -4340,7 +5500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -4546,7 +5706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -4752,7 +5912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -4958,7 +6118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -5164,7 +6324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -5370,7 +6530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -5576,7 +6736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -5791,7 +6951,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -5806,7 +6966,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -6012,7 +7172,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -6218,7 +7378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -6424,7 +7584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -6630,7 +7790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -6836,7 +7996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -7042,7 +8202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -7248,7 +8408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -7454,7 +8614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -7660,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -7875,7 +9035,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -7890,7 +9050,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -8096,7 +9256,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -8113,7 +9273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -8319,7 +9479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -8336,7 +9496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -8353,7 +9513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -8370,7 +9530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -8387,7 +9547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -8404,7 +9564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -8421,7 +9581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -8447,7 +9607,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -8462,7 +9622,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -8668,7 +9828,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -8685,7 +9845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -8702,7 +9862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -8719,7 +9879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -8736,7 +9896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -8753,7 +9913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -8770,7 +9930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -8787,7 +9947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -8804,7 +9964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -8830,7 +9990,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -8845,7 +10005,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -9051,7 +10211,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -9068,7 +10228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -9085,7 +10245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -9102,7 +10262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -9308,7 +10468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -9325,7 +10485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -9342,7 +10502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -9359,7 +10519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -9376,7 +10536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -9402,7 +10562,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -9417,7 +10577,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -9623,7 +10783,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -9640,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -9657,7 +10817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -9674,7 +10834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -9691,7 +10851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -9708,7 +10868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -9725,7 +10885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -9742,7 +10902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -9759,7 +10919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -9785,7 +10945,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -9800,7 +10960,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -10006,7 +11166,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -10212,7 +11372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -10418,7 +11578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -10624,7 +11784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -10830,7 +11990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -11036,7 +12196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -11242,7 +12402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -11448,7 +12608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -11654,7 +12814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -11869,7 +13029,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -11884,7 +13044,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -12090,7 +13250,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -12296,7 +13456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -12502,7 +13662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -12708,7 +13868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -12914,7 +14074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -13120,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -13326,7 +14486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -13532,7 +14692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -13738,7 +14898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -13953,7 +15113,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -13968,7 +15128,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -14174,7 +15334,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -14191,7 +15351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -14208,7 +15368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -14225,7 +15385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -14242,7 +15402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -14259,7 +15419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -14276,7 +15436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -14293,7 +15453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -14310,7 +15470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -14525,14 +15685,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -14542,8 +15702,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -14553,8 +15713,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="9"/>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -14562,8 +15722,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9"/>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
@@ -14571,8 +15731,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="9"/>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -14580,8 +15740,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="9"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -14589,8 +15749,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="9"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -14598,8 +15758,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
       <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
@@ -14607,8 +15767,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="9"/>
       <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
@@ -14616,8 +15776,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="9"/>
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
@@ -14625,8 +15785,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="9"/>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
@@ -14634,8 +15794,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="9"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -14643,8 +15803,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
       <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
@@ -14652,8 +15812,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
       <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
@@ -14661,8 +15821,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="9"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -14670,8 +15830,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="9"/>
       <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
@@ -14679,8 +15839,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="10"/>
       <c r="B17" s="5" t="s">
         <v>34</v>
       </c>
@@ -14688,19 +15848,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
     </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>37</v>
       </c>
@@ -14711,7 +15871,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="3" t="s">
         <v>40</v>
@@ -14720,8 +15880,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="11"/>
       <c r="B22" s="5" t="s">
         <v>42</v>
       </c>
@@ -14729,8 +15889,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -14740,8 +15900,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="9"/>
       <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
@@ -14749,8 +15909,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="9"/>
       <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
@@ -14758,8 +15918,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="9"/>
       <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
@@ -14767,8 +15927,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="9"/>
       <c r="B27" s="3" t="s">
         <v>53</v>
       </c>
@@ -14776,8 +15936,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="9"/>
       <c r="B28" s="3" t="s">
         <v>55</v>
       </c>
@@ -14785,8 +15945,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="9"/>
       <c r="B29" s="3" t="s">
         <v>57</v>
       </c>
@@ -14794,8 +15954,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="9"/>
       <c r="B30" s="3" t="s">
         <v>59</v>
       </c>
@@ -14803,8 +15963,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="9"/>
       <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
@@ -14812,8 +15972,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="9"/>
       <c r="B32" s="3" t="s">
         <v>63</v>
       </c>
@@ -14821,8 +15981,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="9"/>
       <c r="B33" s="3" t="s">
         <v>65</v>
       </c>
@@ -14830,8 +15990,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="9"/>
       <c r="B34" s="3" t="s">
         <v>67</v>
       </c>
@@ -14839,8 +15999,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="9"/>
       <c r="B35" s="3" t="s">
         <v>69</v>
       </c>
@@ -14848,8 +16008,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="9"/>
       <c r="B36" s="3" t="s">
         <v>71</v>
       </c>
@@ -14857,8 +16017,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="9"/>
       <c r="B37" s="3" t="s">
         <v>73</v>
       </c>
@@ -14866,8 +16026,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
       <c r="B38" s="3" t="s">
         <v>75</v>
       </c>
@@ -14875,8 +16035,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
       <c r="B39" s="3" t="s">
         <v>77</v>
       </c>
@@ -14884,8 +16044,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="9"/>
       <c r="B40" s="3" t="s">
         <v>79</v>
       </c>
@@ -14893,8 +16053,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="9"/>
       <c r="B41" s="3" t="s">
         <v>81</v>
       </c>
@@ -14902,8 +16062,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
       <c r="B42" s="3" t="s">
         <v>83</v>
       </c>
@@ -14911,8 +16071,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
       <c r="B43" s="3" t="s">
         <v>85</v>
       </c>
@@ -14920,8 +16080,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="11"/>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="10"/>
       <c r="B44" s="5" t="s">
         <v>87</v>
       </c>
@@ -14929,8 +16089,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
         <v>89</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -14940,8 +16100,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="9"/>
       <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
@@ -14949,8 +16109,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="9"/>
       <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
@@ -14958,8 +16118,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="9"/>
       <c r="B48" s="3" t="s">
         <v>96</v>
       </c>
@@ -14967,8 +16127,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="9"/>
       <c r="B49" s="3" t="s">
         <v>98</v>
       </c>
@@ -14976,8 +16136,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="9"/>
       <c r="B50" s="3" t="s">
         <v>100</v>
       </c>
@@ -14985,8 +16145,8 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="10"/>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="9"/>
       <c r="B51" s="3" t="s">
         <v>102</v>
       </c>
@@ -14994,8 +16154,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="9"/>
       <c r="B52" s="3" t="s">
         <v>104</v>
       </c>
@@ -15003,8 +16163,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="9"/>
       <c r="B53" s="3" t="s">
         <v>106</v>
       </c>
@@ -15012,8 +16172,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10"/>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="9"/>
       <c r="B54" s="3" t="s">
         <v>108</v>
       </c>
@@ -15021,8 +16181,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="10"/>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="9"/>
       <c r="B55" s="3" t="s">
         <v>110</v>
       </c>
@@ -15030,8 +16190,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="10"/>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="9"/>
       <c r="B56" s="3" t="s">
         <v>112</v>
       </c>
@@ -15039,8 +16199,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="10"/>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="9"/>
       <c r="B57" s="3" t="s">
         <v>114</v>
       </c>
@@ -15048,8 +16208,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="10"/>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="9"/>
       <c r="B58" s="3" t="s">
         <v>116</v>
       </c>
@@ -15057,8 +16217,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="10"/>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="9"/>
       <c r="B59" s="3" t="s">
         <v>118</v>
       </c>
@@ -15066,8 +16226,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="10"/>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="9"/>
       <c r="B60" s="3" t="s">
         <v>120</v>
       </c>
@@ -15075,8 +16235,8 @@
         <v>121</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="9"/>
       <c r="B61" s="3" t="s">
         <v>122</v>
       </c>
@@ -15084,8 +16244,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10"/>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="9"/>
       <c r="B62" s="3" t="s">
         <v>124</v>
       </c>
@@ -15093,8 +16253,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="10"/>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="9"/>
       <c r="B63" s="3" t="s">
         <v>126</v>
       </c>
@@ -15102,8 +16262,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="10"/>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="9"/>
       <c r="B64" s="3" t="s">
         <v>128</v>
       </c>
@@ -15111,8 +16271,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="10"/>
       <c r="B65" s="5" t="s">
         <v>130</v>
       </c>
@@ -15137,7 +16297,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -15152,7 +16312,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -15358,7 +16518,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -15375,7 +16535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -15581,7 +16741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -15598,7 +16758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -15804,7 +16964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -15821,7 +16981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -15838,7 +16998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -15855,7 +17015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -15872,7 +17032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -16087,7 +17247,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -16102,7 +17262,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -16308,7 +17468,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -16325,7 +17485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -16342,7 +17502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -16359,7 +17519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -16376,7 +17536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -16393,7 +17553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -16410,7 +17570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -16427,7 +17587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -16444,7 +17604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -16470,7 +17630,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -16485,7 +17645,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -16691,7 +17851,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -16708,7 +17868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -16725,7 +17885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -16742,7 +17902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -16759,7 +17919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -16776,7 +17936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -16793,7 +17953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -16810,7 +17970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -16827,7 +17987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -16853,7 +18013,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -16868,7 +18028,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -17074,7 +18234,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -17091,7 +18251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -17108,7 +18268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -17125,7 +18285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -17142,7 +18302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -17159,7 +18319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -17176,7 +18336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -17193,7 +18353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -17210,7 +18370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -17236,7 +18396,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -17251,7 +18411,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -17457,7 +18617,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -17474,7 +18634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -17491,7 +18651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -17508,7 +18668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -17525,7 +18685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -17542,7 +18702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -17559,7 +18719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -17576,7 +18736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -17593,7 +18753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -17619,7 +18779,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CA10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -17645,7 +18805,7 @@
     <col min="77" max="79" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -17884,7 +19044,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -18120,7 +19280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -18356,7 +19516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -18592,7 +19752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -18828,7 +19988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -19064,7 +20224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -19300,7 +20460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -19536,7 +20696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -19772,7 +20932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -20017,7 +21177,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -20032,7 +21192,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -20238,7 +21398,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -20444,7 +21604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -20650,7 +21810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -20856,7 +22016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -21062,7 +22222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -21268,7 +22428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -21474,7 +22634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -21680,7 +22840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -21886,7 +23046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -22101,7 +23261,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -22116,7 +23276,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -22322,7 +23482,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -22339,7 +23499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -22356,7 +23516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -22373,7 +23533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -22390,7 +23550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -22407,7 +23567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -22424,7 +23584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -22441,7 +23601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -22458,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -22673,7 +23833,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -22688,7 +23848,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -22894,7 +24054,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -23100,7 +24260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -23306,7 +24466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -23323,7 +24483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -23529,7 +24689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -23546,7 +24706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -23563,7 +24723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -23769,7 +24929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -23975,7 +25135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -24001,7 +25161,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -24016,7 +25176,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -24222,7 +25382,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -24239,7 +25399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -24256,7 +25416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -24462,7 +25622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -24668,7 +25828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -24874,7 +26034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -25080,7 +26240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -25097,7 +26257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -25114,7 +26274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -25329,7 +26489,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -25344,7 +26504,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -25550,7 +26710,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -25756,7 +26916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -25773,7 +26933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -25790,7 +26950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -25807,7 +26967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -25824,7 +26984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -25841,7 +27001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -25858,7 +27018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -25875,7 +27035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
@@ -25901,7 +27061,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:BP10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -25916,7 +27076,7 @@
     <col min="66" max="68" width="11" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -26122,7 +27282,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>569</v>
       </c>
@@ -26139,7 +27299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>570</v>
       </c>
@@ -26345,7 +27505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>571</v>
       </c>
@@ -26551,7 +27711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>572</v>
       </c>
@@ -26568,7 +27728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>573</v>
       </c>
@@ -26585,7 +27745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>574</v>
       </c>
@@ -26791,7 +27951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>575</v>
       </c>
@@ -26997,7 +28157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>576</v>
       </c>
@@ -27014,7 +28174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>592</v>
       </c>
